--- a/manuscript_material/supplementary/Supplementary_Data_3_parameter_substitutions.xlsx
+++ b/manuscript_material/supplementary/Supplementary_Data_3_parameter_substitutions.xlsx
@@ -443,14 +443,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Supplementary Data 3 | 2,085 detected parameter substitutions (first substituted value per tool-run call)</t>
+          <t>Supplementary Data 3 | 2,085 parameter substitutions with a replaced value (first per tool-run call)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>For every Codex-harness tool-run call whose parameter provenance reported an explicit value substitution (statuses validation_parameter_mismatch or parameter_mismatch), the first substituted parameter path with its requested and resolved values. Calls in which a requested path was only missing from the resolved state are counted in Supplementary Table 37 but have no resolved value to list.</t>
+          <t>For every tool-run call with a Codex execution trace in which a requested parameter value was replaced (parameter substitution, blocked or executed), the first replaced parameter with the value requested by the agent and the value Galaxy resolved. Calls in which a requested value was only dropped are counted in Supplementary Table 37 but have no resolved value to list.</t>
         </is>
       </c>
     </row>
@@ -470,7 +470,7 @@
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
@@ -489,7 +489,7 @@
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>tool</t>
+          <t>galaxy_tool</t>
         </is>
       </c>
       <c r="D1" s="3" t="inlineStr">
@@ -499,12 +499,12 @@
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>requested_value</t>
+          <t>value_requested</t>
         </is>
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>resolved_value</t>
+          <t>value_resolved</t>
         </is>
       </c>
     </row>
